--- a/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -62,6 +76,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -77,6 +98,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -92,6 +120,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -107,6 +142,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -122,6 +164,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -137,6 +186,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -152,6 +208,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -167,6 +230,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -182,6 +252,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -199,10 +276,35 @@
     <t>物流商明细字段</t>
   </si>
   <si>
-    <t>数大臣单据字段</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数大臣单据字段</t>
+    </r>
+  </si>
+  <si>
+    <t>数大臣字段明细</t>
   </si>
   <si>
     <t>导入更新,导入新增(按原单),导入新增(按新单)</t>
+  </si>
+  <si>
+    <t>运费/物流费用</t>
   </si>
 </sst>
 </file>
@@ -215,7 +317,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +331,18 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF909399"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -693,137 +807,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -831,6 +945,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1179,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1190,7 +1308,7 @@
     <col min="18" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1227,19 +1345,26 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="I2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:15">
       <c r="K4" s="2"/>
     </row>
-    <row r="5" customFormat="1" spans="1:13">
+    <row r="5" customFormat="1" spans="1:15">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1254,14 +1379,12 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" customFormat="1"/>
-    <row r="7" customFormat="1"/>
-    <row r="8" customFormat="1" spans="1:13">
+    <row r="8" customFormat="1" spans="1:15">
       <c r="K8" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 J1 I$1:I$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:J1 I2:I1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"API,线下表格"</formula1>
     </dataValidation>

--- a/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>数大臣字段明细</t>
+  </si>
+  <si>
+    <t>是否识别单号</t>
+  </si>
+  <si>
+    <t>是否绝对值处理</t>
   </si>
   <si>
     <t>导入更新,导入新增(按原单),导入新增(按新单)</t>
@@ -317,7 +323,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,12 +343,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF909399"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -807,137 +807,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,7 +948,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1297,7 +1296,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1308,7 +1307,7 @@
     <col min="18" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,20 +1350,25 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4"/>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="I2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="K4" s="2"/>
     </row>
-    <row r="5" customFormat="1" spans="1:15">
+    <row r="5" customFormat="1" spans="1:16">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1379,17 +1383,20 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="8" customFormat="1" spans="1:15">
+    <row r="8" customFormat="1" spans="1:16">
       <c r="K8" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:J1 I2:I1048576"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"API,线下表格"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
       <formula1>"启用,停用"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O$1:P$1048576">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/cfgLogisticsCostTemplate.xlsx
@@ -54,24 +54,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>配置单据</t>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>识别维度</t>
     </r>
   </si>
   <si>
